--- a/artfynd/A 806-2022 artfynd.xlsx
+++ b/artfynd/A 806-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 806-2022 artfynd.xlsx
+++ b/artfynd/A 806-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108284600</v>
+        <v>108284592</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446148.6368650644</v>
+        <v>445894</v>
       </c>
       <c r="R2" t="n">
-        <v>7067055.75327965</v>
+        <v>7067009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108284599</v>
+        <v>108284593</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445958.5950188721</v>
+        <v>445902</v>
       </c>
       <c r="R3" t="n">
-        <v>7067152.508404375</v>
+        <v>7067012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108284602</v>
+        <v>108284598</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445980.2900455986</v>
+        <v>445865</v>
       </c>
       <c r="R4" t="n">
-        <v>7067175.623724443</v>
+        <v>7067170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +955,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1034,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108284607</v>
+        <v>108284599</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446215.3276595616</v>
+        <v>445958</v>
       </c>
       <c r="R5" t="n">
-        <v>7067323.603611789</v>
+        <v>7067152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,19 +1059,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108284603</v>
+        <v>108284600</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446027.4779930418</v>
+        <v>446149</v>
       </c>
       <c r="R6" t="n">
-        <v>7067236.412867477</v>
+        <v>7067056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1165,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1274,15 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108284592</v>
+        <v>108284601</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,18 +1230,16 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445894.4498316488</v>
+        <v>445990</v>
       </c>
       <c r="R7" t="n">
-        <v>7067008.694442076</v>
+        <v>7067193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,24 +1269,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,15 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108284601</v>
+        <v>108284602</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445989.901436542</v>
+        <v>445980</v>
       </c>
       <c r="R8" t="n">
-        <v>7067192.741834572</v>
+        <v>7067176</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,19 +1373,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1514,15 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108284598</v>
+        <v>108284603</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,16 +1438,18 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445864.3809054123</v>
+        <v>446028</v>
       </c>
       <c r="R9" t="n">
-        <v>7067170.076861309</v>
+        <v>7067236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,24 +1479,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108284609</v>
+        <v>108284604</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,16 +1544,18 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445935.5556236911</v>
+        <v>446056</v>
       </c>
       <c r="R10" t="n">
-        <v>7067232.225898764</v>
+        <v>7067225</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,24 +1585,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,12 +1622,7 @@
         <v>108284605</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446167.0935677667</v>
+        <v>446167</v>
       </c>
       <c r="R11" t="n">
-        <v>7067279.227252661</v>
+        <v>7067279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,19 +1689,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1871,15 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108284593</v>
+        <v>108284607</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445902.4882497647</v>
+        <v>446215</v>
       </c>
       <c r="R12" t="n">
-        <v>7067011.658803724</v>
+        <v>7067323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,19 +1793,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1993,12 +1830,7 @@
         <v>108284608</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446168.1291184587</v>
+        <v>446168</v>
       </c>
       <c r="R13" t="n">
-        <v>7067339.917908906</v>
+        <v>7067340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,19 +1897,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2109,15 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108284648</v>
+        <v>108284609</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445363.18742266</v>
+        <v>445936</v>
       </c>
       <c r="R14" t="n">
-        <v>7066414.191571997</v>
+        <v>7067232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,19 +2001,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2228,15 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108284650</v>
+        <v>108284648</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445269.5108960064</v>
+        <v>445363</v>
       </c>
       <c r="R15" t="n">
-        <v>7066310.317866464</v>
+        <v>7066414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,19 +2105,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2350,12 +2142,7 @@
         <v>108284649</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445327.1088446653</v>
+        <v>445327</v>
       </c>
       <c r="R16" t="n">
-        <v>7066406.837734086</v>
+        <v>7066407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,19 +2211,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2468,15 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108284626</v>
+        <v>108284650</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445491.413390337</v>
+        <v>445270</v>
       </c>
       <c r="R17" t="n">
-        <v>7066642.902210473</v>
+        <v>7066310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,19 +2315,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2587,15 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108284595</v>
+        <v>108284582</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445777.1115666777</v>
+        <v>445827</v>
       </c>
       <c r="R18" t="n">
-        <v>7067101.114132132</v>
+        <v>7066421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,19 +2419,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2706,15 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108284617</v>
+        <v>108284584</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445701.9486558163</v>
+        <v>445900</v>
       </c>
       <c r="R19" t="n">
-        <v>7066988.069889454</v>
+        <v>7066586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,19 +2523,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2825,15 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>108284610</v>
+        <v>108284585</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,18 +2588,16 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445812.8195369632</v>
+        <v>445917</v>
       </c>
       <c r="R20" t="n">
-        <v>7067216.605861456</v>
+        <v>7066642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,24 +2627,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,15 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>108284628</v>
+        <v>108284586</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,16 +2692,18 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445571.6780973275</v>
+        <v>445913</v>
       </c>
       <c r="R21" t="n">
-        <v>7066356.068251712</v>
+        <v>7066637</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3021,24 +2733,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3068,12 +2770,7 @@
         <v>108284587</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3107,10 +2804,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446065.8891807119</v>
+        <v>446066</v>
       </c>
       <c r="R22" t="n">
-        <v>7066731.868754654</v>
+        <v>7066732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3140,19 +2837,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3184,15 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>108284645</v>
+        <v>108284588</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,18 +2902,16 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445498.396078321</v>
+        <v>446079</v>
       </c>
       <c r="R23" t="n">
-        <v>7066379.05269401</v>
+        <v>7066711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3261,24 +2941,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3305,15 +2975,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108284640</v>
+        <v>108284589</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,16 +3006,18 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445485.1060079595</v>
+        <v>446151</v>
       </c>
       <c r="R24" t="n">
-        <v>7066174.932597376</v>
+        <v>7066878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3380,24 +3047,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,12 +3084,7 @@
         <v>108284590</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143.0789850811</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>7066886.112501987</v>
+        <v>7066886</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,19 +3153,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3545,15 +3187,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>108284625</v>
+        <v>108284591</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,18 +3218,16 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445440.3918682674</v>
+        <v>446124</v>
       </c>
       <c r="R26" t="n">
-        <v>7066695.197414016</v>
+        <v>7066884</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,24 +3257,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3666,15 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108284646</v>
+        <v>108284594</v>
       </c>
       <c r="B27" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3702,16 +3322,18 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445485.6202318262</v>
+        <v>445765</v>
       </c>
       <c r="R27" t="n">
-        <v>7066384.592460061</v>
+        <v>7067085</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3741,24 +3363,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3785,15 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>108284637</v>
+        <v>108284595</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3821,18 +3428,16 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445521.5771305248</v>
+        <v>445777</v>
       </c>
       <c r="R28" t="n">
-        <v>7066153.468257049</v>
+        <v>7067101</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3862,24 +3467,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3906,15 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>108284623</v>
+        <v>108284596</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3942,16 +3532,18 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445622.4880229445</v>
+        <v>445804</v>
       </c>
       <c r="R29" t="n">
-        <v>7066677.428239473</v>
+        <v>7067154</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3981,24 +3573,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4025,15 +3607,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108284642</v>
+        <v>108284597</v>
       </c>
       <c r="B30" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,10 +3646,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445525.3634059895</v>
+        <v>445840</v>
       </c>
       <c r="R30" t="n">
-        <v>7066321.406034276</v>
+        <v>7067151</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4102,19 +3679,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4146,15 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>108284632</v>
+        <v>108284610</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,16 +3744,18 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445573.746970184</v>
+        <v>445813</v>
       </c>
       <c r="R31" t="n">
-        <v>7066192.907535586</v>
+        <v>7067217</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4221,24 +3785,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4265,15 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>108284612</v>
+        <v>108284611</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,18 +3850,16 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445715.8214755537</v>
+        <v>445752</v>
       </c>
       <c r="R32" t="n">
-        <v>7067149.585549216</v>
+        <v>7067171</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,24 +3889,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4386,15 +3923,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>108284643</v>
+        <v>108284612</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4430,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445538.9044514265</v>
+        <v>445716</v>
       </c>
       <c r="R33" t="n">
-        <v>7066334.470368772</v>
+        <v>7067149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4463,19 +3995,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4507,15 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>108284629</v>
+        <v>108284613</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4543,16 +4060,18 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445577.922887311</v>
+        <v>445714</v>
       </c>
       <c r="R34" t="n">
-        <v>7066254.894958487</v>
+        <v>7067130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4582,24 +4101,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4626,15 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>108284635</v>
+        <v>108284614</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4668,10 +4172,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445554.0248176802</v>
+        <v>445569</v>
       </c>
       <c r="R35" t="n">
-        <v>7066104.589225682</v>
+        <v>7067012</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4701,19 +4205,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4745,15 +4239,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>108284633</v>
+        <v>108284615</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4781,18 +4270,16 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445559.4946398541</v>
+        <v>445569</v>
       </c>
       <c r="R36" t="n">
-        <v>7066138.628676434</v>
+        <v>7067003</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4822,24 +4309,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4866,15 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>108284588</v>
+        <v>108284616</v>
       </c>
       <c r="B37" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4902,16 +4374,18 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446079.2944983342</v>
+        <v>445645</v>
       </c>
       <c r="R37" t="n">
-        <v>7066711.252045063</v>
+        <v>7066982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4941,24 +4415,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4985,15 +4449,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>108284597</v>
+        <v>108284617</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,18 +4480,16 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445839.6481800398</v>
+        <v>445702</v>
       </c>
       <c r="R38" t="n">
-        <v>7067151.002761966</v>
+        <v>7066988</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5062,24 +4519,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5106,15 +4553,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>108284630</v>
+        <v>108284618</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,16 +4584,18 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445582.2455927092</v>
+        <v>445712</v>
       </c>
       <c r="R39" t="n">
-        <v>7066248.171261234</v>
+        <v>7066970</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5181,24 +4625,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5225,15 +4659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>108284594</v>
+        <v>108284619</v>
       </c>
       <c r="B40" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5261,18 +4690,16 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445764.4086695811</v>
+        <v>445744</v>
       </c>
       <c r="R40" t="n">
-        <v>7067084.935577983</v>
+        <v>7066956</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5302,24 +4729,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5346,15 +4763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>108284591</v>
+        <v>108284620</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5382,16 +4794,18 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446123.9721239914</v>
+        <v>445747</v>
       </c>
       <c r="R41" t="n">
-        <v>7066884.665925723</v>
+        <v>7066953</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5421,24 +4835,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5465,15 +4869,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>108284584</v>
+        <v>108284621</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5507,10 +4906,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445899.6251435542</v>
+        <v>445759</v>
       </c>
       <c r="R42" t="n">
-        <v>7066585.793257814</v>
+        <v>7066842</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5540,19 +4939,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5584,15 +4973,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>108284611</v>
+        <v>108284622</v>
       </c>
       <c r="B43" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5626,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445752.5703320839</v>
+        <v>445696</v>
       </c>
       <c r="R43" t="n">
-        <v>7067170.667837338</v>
+        <v>7066753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5659,19 +5043,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5703,15 +5077,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>108284631</v>
+        <v>108284623</v>
       </c>
       <c r="B44" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5739,18 +5108,16 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445591.029903172</v>
+        <v>445623</v>
       </c>
       <c r="R44" t="n">
-        <v>7066191.279708331</v>
+        <v>7066677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5780,24 +5147,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5824,15 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>108284621</v>
+        <v>108284624</v>
       </c>
       <c r="B45" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5860,16 +5212,18 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445758.4608000555</v>
+        <v>445603</v>
       </c>
       <c r="R45" t="n">
-        <v>7066842.176771935</v>
+        <v>7066747</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5899,24 +5253,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5943,15 +5287,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>108284641</v>
+        <v>108284625</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5987,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445551.4063951484</v>
+        <v>445441</v>
       </c>
       <c r="R46" t="n">
-        <v>7066235.848016623</v>
+        <v>7066695</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6020,19 +5359,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6064,15 +5393,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>108284644</v>
+        <v>108284626</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6106,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445522.9457421207</v>
+        <v>445491</v>
       </c>
       <c r="R47" t="n">
-        <v>7066361.341655433</v>
+        <v>7066643</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6139,19 +5463,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6183,15 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>108284586</v>
+        <v>108284627</v>
       </c>
       <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6219,18 +5528,16 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445912.9292284362</v>
+        <v>445586</v>
       </c>
       <c r="R48" t="n">
-        <v>7066636.979384066</v>
+        <v>7066431</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6260,24 +5567,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6304,15 +5601,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>108284624</v>
+        <v>108284628</v>
       </c>
       <c r="B49" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6340,18 +5632,16 @@
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445602.8345933859</v>
+        <v>445572</v>
       </c>
       <c r="R49" t="n">
-        <v>7066747.351407844</v>
+        <v>7066356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6381,24 +5671,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6425,15 +5705,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>108284589</v>
+        <v>108284629</v>
       </c>
       <c r="B50" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6461,18 +5736,16 @@
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446150.92844487</v>
+        <v>445578</v>
       </c>
       <c r="R50" t="n">
-        <v>7066878.00118422</v>
+        <v>7066255</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6502,24 +5775,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6546,15 +5809,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>108284647</v>
+        <v>108284630</v>
       </c>
       <c r="B51" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6588,10 +5846,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445482.2083095369</v>
+        <v>445582</v>
       </c>
       <c r="R51" t="n">
-        <v>7066392.630058168</v>
+        <v>7066248</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6621,19 +5879,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6665,15 +5913,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>108284634</v>
+        <v>108284631</v>
       </c>
       <c r="B52" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,16 +5944,18 @@
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445552.1274977272</v>
+        <v>445591</v>
       </c>
       <c r="R52" t="n">
-        <v>7066097.529170022</v>
+        <v>7066191</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6740,24 +5985,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6784,15 +6019,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>108284585</v>
+        <v>108284632</v>
       </c>
       <c r="B53" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6826,10 +6056,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445917.0134450899</v>
+        <v>445574</v>
       </c>
       <c r="R53" t="n">
-        <v>7066642.228046751</v>
+        <v>7066193</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6859,19 +6089,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6903,15 +6123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>108284616</v>
+        <v>108284633</v>
       </c>
       <c r="B54" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6947,10 +6162,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445645.0345532791</v>
+        <v>445560</v>
       </c>
       <c r="R54" t="n">
-        <v>7066981.515821394</v>
+        <v>7066139</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6980,24 +6195,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7024,15 +6229,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>108284618</v>
+        <v>108284634</v>
       </c>
       <c r="B55" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7060,18 +6260,16 @@
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445711.8548176893</v>
+        <v>445552</v>
       </c>
       <c r="R55" t="n">
-        <v>7066970.615606768</v>
+        <v>7066098</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7101,24 +6299,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7145,15 +6333,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>108284613</v>
+        <v>108284635</v>
       </c>
       <c r="B56" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7181,18 +6364,16 @@
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445714.1629007211</v>
+        <v>445554</v>
       </c>
       <c r="R56" t="n">
-        <v>7067130.558521944</v>
+        <v>7066105</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7222,24 +6403,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7269,12 +6440,7 @@
         <v>108284636</v>
       </c>
       <c r="B57" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,10 +6474,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445542.9463054503</v>
+        <v>445543</v>
       </c>
       <c r="R57" t="n">
-        <v>7066105.666935753</v>
+        <v>7066106</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7341,19 +6507,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7382,6 +6538,1167 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>108284637</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>445521</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7066153</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>108284638</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>445479</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7066179</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>108284640</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>445485</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7066175</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>108284641</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>445551</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7066236</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>108284642</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>445525</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7066321</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>ringhack gamla</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>108284643</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>445539</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7066334</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>ringhack gamla</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>108284644</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>445523</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7066361</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>108284645</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>445499</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7066379</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>ringhack gamla</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>108284646</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>445485</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7066385</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>108284647</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>445482</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7066393</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>108284667</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>445738</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7066958</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 806-2022 artfynd.xlsx
+++ b/artfynd/A 806-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284599</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284602</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284603</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284604</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284605</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284607</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284608</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284609</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2206,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284648</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2346,6 +2426,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2450,6 +2535,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284582</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2554,6 +2644,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284584</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2658,6 +2753,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284585</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2764,6 +2864,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284586</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2868,6 +2973,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284587</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2972,6 +3082,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284588</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3076,6 +3191,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284621</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,6 +3300,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3284,6 +3409,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284623</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3390,6 +3520,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284624</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3496,6 +3631,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3600,6 +3740,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3704,6 +3849,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3808,6 +3958,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284628</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3912,6 +4067,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284629</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284630</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4122,6 +4287,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284631</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4226,6 +4396,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284632</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4332,6 +4507,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284633</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4436,6 +4616,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284634</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4540,6 +4725,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284635</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4644,6 +4834,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284636</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4750,6 +4945,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284637</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4856,6 +5056,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284638</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4960,6 +5165,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284640</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5066,6 +5276,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284641</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5172,6 +5387,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284642</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5278,6 +5498,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284643</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5382,6 +5607,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284644</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5488,6 +5718,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284645</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5592,6 +5827,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284646</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5696,6 +5936,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284647</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5802,6 +6047,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284589</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5908,6 +6158,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284590</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6012,6 +6267,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284591</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6118,6 +6378,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284594</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6222,6 +6487,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284595</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6328,6 +6598,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284596</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6434,6 +6709,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284597</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6540,6 +6820,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284610</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6644,6 +6929,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284611</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6750,6 +7040,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284612</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6856,6 +7151,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284613</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6960,6 +7260,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284614</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7064,6 +7369,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284615</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7170,6 +7480,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284616</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7274,6 +7589,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284617</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7380,6 +7700,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284618</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7484,6 +7809,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284619</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7590,6 +7920,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284620</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7699,8 +8034,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>